--- a/mockdata/Epicollect_Metadata.xlsx
+++ b/mockdata/Epicollect_Metadata.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="49">
   <si>
     <t>Site ID</t>
   </si>
@@ -31,6 +31,12 @@
     <t>Sample ID</t>
   </si>
   <si>
+    <t>Sample Name</t>
+  </si>
+  <si>
+    <t>Analysis Type</t>
+  </si>
+  <si>
     <t>Trip ID</t>
   </si>
   <si>
@@ -55,7 +61,7 @@
     <t>A10</t>
   </si>
   <si>
-    <t>Farm A Dispatch</t>
+    <t>Pretoria</t>
   </si>
   <si>
     <t>Apies River</t>
@@ -70,6 +76,12 @@
     <t>SAMP-001</t>
   </si>
   <si>
+    <t>AP-01-MAY</t>
+  </si>
+  <si>
+    <t>Metagenomics</t>
+  </si>
+  <si>
     <t>Trip 1</t>
   </si>
   <si>
@@ -88,7 +100,7 @@
     <t>B26</t>
   </si>
   <si>
-    <t>Farm B Pivot 1</t>
+    <t>Hammanskraal</t>
   </si>
   <si>
     <t>-25.750</t>
@@ -100,6 +112,12 @@
     <t>SAMP-002</t>
   </si>
   <si>
+    <t>AP-02-MAY</t>
+  </si>
+  <si>
+    <t>WGS</t>
+  </si>
+  <si>
     <t>19.1</t>
   </si>
   <si>
@@ -112,7 +130,7 @@
     <t>B27</t>
   </si>
   <si>
-    <t>Farm B Pivot 2</t>
+    <t>Tshwane</t>
   </si>
   <si>
     <t>-25.752</t>
@@ -122,6 +140,9 @@
   </si>
   <si>
     <t>SAMP-003</t>
+  </si>
+  <si>
+    <t>AP-03-JUL</t>
   </si>
   <si>
     <t>Trip 2</t>
@@ -146,7 +167,7 @@
   <numFmts count="1">
     <numFmt numFmtId="0" formatCode="General"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <color indexed="8"/>
@@ -173,14 +194,8 @@
       <color indexed="9"/>
       <name val="Helvetica"/>
     </font>
-    <font>
-      <b val="1"/>
-      <sz val="10"/>
-      <color indexed="8"/>
-      <name val="Helvetica Neue"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -193,115 +208,13 @@
         <bgColor auto="1"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="13"/>
-        <bgColor auto="1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="14"/>
-        <bgColor auto="1"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="8">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="11"/>
-      </left>
-      <right style="thin">
-        <color indexed="11"/>
-      </right>
-      <top style="thin">
-        <color indexed="11"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="12"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="11"/>
-      </left>
-      <right style="thin">
-        <color indexed="12"/>
-      </right>
-      <top style="thin">
-        <color indexed="12"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="11"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="12"/>
-      </left>
-      <right style="thin">
-        <color indexed="11"/>
-      </right>
-      <top style="thin">
-        <color indexed="12"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="11"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="11"/>
-      </left>
-      <right style="thin">
-        <color indexed="11"/>
-      </right>
-      <top style="thin">
-        <color indexed="12"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="11"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="11"/>
-      </left>
-      <right style="thin">
-        <color indexed="12"/>
-      </right>
-      <top style="thin">
-        <color indexed="11"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="11"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="12"/>
-      </left>
-      <right style="thin">
-        <color indexed="11"/>
-      </right>
-      <top style="thin">
-        <color indexed="11"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="11"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -325,7 +238,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -335,37 +248,13 @@
     <xf numFmtId="49" fontId="3" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="4" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="4" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -388,9 +277,6 @@
       <rgbColor rgb="ff1f1f1f"/>
       <rgbColor rgb="ffefefef"/>
       <rgbColor rgb="ffa5a5a5"/>
-      <rgbColor rgb="ff3f3f3f"/>
-      <rgbColor rgb="ffffffff"/>
-      <rgbColor rgb="ffdbdbdb"/>
     </indexedColors>
   </colors>
 </styleSheet>
@@ -1422,11 +1308,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:M22"/>
-  <sheetFormatPr defaultColWidth="16.3333" defaultRowHeight="19.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:O22"/>
+  <sheetFormatPr defaultColWidth="16.3333" defaultRowHeight="13.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="13" width="16.3516" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="16.3516" style="1" customWidth="1"/>
+    <col min="1" max="15" width="16.3516" style="1" customWidth="1"/>
+    <col min="16" max="16384" width="16.3516" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="60.55" customHeight="1">
@@ -1469,399 +1355,459 @@
       <c r="M1" t="s" s="2">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" ht="60.55" customHeight="1">
+      <c r="N1" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" ht="74.55" customHeight="1">
       <c r="A2" t="s" s="3">
-        <v>13</v>
-      </c>
-      <c r="B2" t="s" s="4">
-        <v>14</v>
-      </c>
-      <c r="C2" t="s" s="5">
         <v>15</v>
       </c>
-      <c r="D2" t="s" s="5">
+      <c r="B2" t="s" s="3">
         <v>16</v>
       </c>
-      <c r="E2" t="s" s="5">
+      <c r="C2" t="s" s="3">
         <v>17</v>
       </c>
-      <c r="F2" t="s" s="5">
+      <c r="D2" t="s" s="3">
         <v>18</v>
       </c>
-      <c r="G2" t="s" s="5">
+      <c r="E2" t="s" s="3">
         <v>19</v>
       </c>
-      <c r="H2" t="s" s="5">
+      <c r="F2" t="s" s="3">
         <v>20</v>
       </c>
-      <c r="I2" t="s" s="5">
+      <c r="G2" t="s" s="3">
         <v>21</v>
       </c>
-      <c r="J2" t="s" s="5">
+      <c r="H2" t="s" s="3">
         <v>22</v>
       </c>
-      <c r="K2" s="6">
+      <c r="I2" t="s" s="3">
+        <v>23</v>
+      </c>
+      <c r="J2" t="s" s="3">
+        <v>24</v>
+      </c>
+      <c r="K2" t="s" s="3">
+        <v>25</v>
+      </c>
+      <c r="L2" t="s" s="3">
+        <v>26</v>
+      </c>
+      <c r="M2" s="4">
         <v>250</v>
       </c>
-      <c r="L2" s="6">
+      <c r="N2" s="4">
         <v>400</v>
       </c>
-      <c r="M2" t="s" s="5">
+      <c r="O2" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" ht="46.35" customHeight="1">
+      <c r="A3" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="B3" t="s" s="3">
+        <v>29</v>
+      </c>
+      <c r="C3" t="s" s="3">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s" s="3">
+        <v>30</v>
+      </c>
+      <c r="E3" t="s" s="3">
+        <v>31</v>
+      </c>
+      <c r="F3" t="s" s="3">
+        <v>32</v>
+      </c>
+      <c r="G3" t="s" s="3">
+        <v>33</v>
+      </c>
+      <c r="H3" t="s" s="3">
+        <v>34</v>
+      </c>
+      <c r="I3" t="s" s="3">
         <v>23</v>
       </c>
-    </row>
-    <row r="3" ht="46.35" customHeight="1">
-      <c r="A3" t="s" s="7">
+      <c r="J3" t="s" s="3">
         <v>24</v>
       </c>
-      <c r="B3" t="s" s="8">
-        <v>25</v>
-      </c>
-      <c r="C3" t="s" s="9">
-        <v>15</v>
-      </c>
-      <c r="D3" t="s" s="9">
-        <v>26</v>
-      </c>
-      <c r="E3" t="s" s="9">
-        <v>27</v>
-      </c>
-      <c r="F3" t="s" s="9">
-        <v>28</v>
-      </c>
-      <c r="G3" t="s" s="9">
-        <v>19</v>
-      </c>
-      <c r="H3" t="s" s="9">
-        <v>20</v>
-      </c>
-      <c r="I3" t="s" s="9">
-        <v>29</v>
-      </c>
-      <c r="J3" t="s" s="9">
-        <v>30</v>
-      </c>
-      <c r="K3" s="10">
+      <c r="K3" t="s" s="3">
+        <v>35</v>
+      </c>
+      <c r="L3" t="s" s="3">
+        <v>36</v>
+      </c>
+      <c r="M3" s="4">
         <v>260</v>
       </c>
-      <c r="L3" s="10">
+      <c r="N3" s="4">
         <v>410</v>
       </c>
-      <c r="M3" t="s" s="9">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" ht="46.35" customHeight="1">
-      <c r="A4" t="s" s="7">
-        <v>32</v>
-      </c>
-      <c r="B4" t="s" s="8">
-        <v>33</v>
-      </c>
-      <c r="C4" t="s" s="9">
-        <v>15</v>
-      </c>
-      <c r="D4" t="s" s="9">
+      <c r="O3" t="s" s="3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" ht="60.35" customHeight="1">
+      <c r="A4" t="s" s="3">
+        <v>38</v>
+      </c>
+      <c r="B4" t="s" s="3">
+        <v>39</v>
+      </c>
+      <c r="C4" t="s" s="3">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s" s="3">
+        <v>40</v>
+      </c>
+      <c r="E4" t="s" s="3">
+        <v>41</v>
+      </c>
+      <c r="F4" t="s" s="3">
+        <v>42</v>
+      </c>
+      <c r="G4" t="s" s="3">
+        <v>43</v>
+      </c>
+      <c r="H4" t="s" s="3">
         <v>34</v>
       </c>
-      <c r="E4" t="s" s="9">
-        <v>35</v>
-      </c>
-      <c r="F4" t="s" s="9">
-        <v>36</v>
-      </c>
-      <c r="G4" t="s" s="9">
-        <v>37</v>
-      </c>
-      <c r="H4" t="s" s="9">
-        <v>38</v>
-      </c>
-      <c r="I4" t="s" s="9">
-        <v>39</v>
-      </c>
-      <c r="J4" t="s" s="9">
-        <v>40</v>
-      </c>
-      <c r="K4" s="10">
+      <c r="I4" t="s" s="3">
+        <v>44</v>
+      </c>
+      <c r="J4" t="s" s="3">
+        <v>45</v>
+      </c>
+      <c r="K4" t="s" s="3">
+        <v>46</v>
+      </c>
+      <c r="L4" t="s" s="3">
+        <v>47</v>
+      </c>
+      <c r="M4" s="4">
         <v>280</v>
       </c>
-      <c r="L4" s="10">
+      <c r="N4" s="4">
         <v>450</v>
       </c>
-      <c r="M4" t="s" s="9">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="5" ht="20.05" customHeight="1">
-      <c r="A5" s="11"/>
-      <c r="B5" s="12"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
-      <c r="I5" s="13"/>
-      <c r="J5" s="13"/>
-      <c r="K5" s="13"/>
-      <c r="L5" s="13"/>
-      <c r="M5" s="13"/>
+      <c r="O4" t="s" s="3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" ht="46.35" customHeight="1">
+      <c r="A5" s="5"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="5"/>
     </row>
     <row r="6" ht="20.05" customHeight="1">
-      <c r="A6" s="11"/>
-      <c r="B6" s="12"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13"/>
-      <c r="L6" s="13"/>
-      <c r="M6" s="13"/>
+      <c r="A6" s="5"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="5"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
     </row>
     <row r="7" ht="20.05" customHeight="1">
-      <c r="A7" s="11"/>
-      <c r="B7" s="12"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="13"/>
-      <c r="K7" s="13"/>
-      <c r="L7" s="13"/>
-      <c r="M7" s="13"/>
+      <c r="A7" s="5"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="5"/>
+      <c r="L7" s="5"/>
+      <c r="M7" s="5"/>
+      <c r="N7" s="5"/>
+      <c r="O7" s="5"/>
     </row>
     <row r="8" ht="20.05" customHeight="1">
-      <c r="A8" s="11"/>
-      <c r="B8" s="12"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="13"/>
-      <c r="I8" s="13"/>
-      <c r="J8" s="13"/>
-      <c r="K8" s="13"/>
-      <c r="L8" s="13"/>
-      <c r="M8" s="13"/>
+      <c r="A8" s="5"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="5"/>
+      <c r="N8" s="5"/>
+      <c r="O8" s="5"/>
     </row>
     <row r="9" ht="20.05" customHeight="1">
-      <c r="A9" s="11"/>
-      <c r="B9" s="12"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13"/>
-      <c r="I9" s="13"/>
-      <c r="J9" s="13"/>
-      <c r="K9" s="13"/>
-      <c r="L9" s="13"/>
-      <c r="M9" s="13"/>
+      <c r="A9" s="5"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="5"/>
+      <c r="L9" s="5"/>
+      <c r="M9" s="5"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="5"/>
     </row>
     <row r="10" ht="20.05" customHeight="1">
-      <c r="A10" s="11"/>
-      <c r="B10" s="12"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="13"/>
-      <c r="J10" s="13"/>
-      <c r="K10" s="13"/>
-      <c r="L10" s="13"/>
-      <c r="M10" s="13"/>
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="5"/>
+      <c r="M10" s="5"/>
+      <c r="N10" s="5"/>
+      <c r="O10" s="5"/>
     </row>
     <row r="11" ht="20.05" customHeight="1">
-      <c r="A11" s="11"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="13"/>
-      <c r="J11" s="13"/>
-      <c r="K11" s="13"/>
-      <c r="L11" s="13"/>
-      <c r="M11" s="13"/>
+      <c r="A11" s="5"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="5"/>
+      <c r="L11" s="5"/>
+      <c r="M11" s="5"/>
+      <c r="N11" s="5"/>
+      <c r="O11" s="5"/>
     </row>
     <row r="12" ht="20.05" customHeight="1">
-      <c r="A12" s="11"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
-      <c r="H12" s="13"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="13"/>
-      <c r="K12" s="13"/>
-      <c r="L12" s="13"/>
-      <c r="M12" s="13"/>
+      <c r="A12" s="5"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="5"/>
+      <c r="L12" s="5"/>
+      <c r="M12" s="5"/>
+      <c r="N12" s="5"/>
+      <c r="O12" s="5"/>
     </row>
     <row r="13" ht="20.05" customHeight="1">
-      <c r="A13" s="11"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="13"/>
-      <c r="I13" s="13"/>
-      <c r="J13" s="13"/>
-      <c r="K13" s="13"/>
-      <c r="L13" s="13"/>
-      <c r="M13" s="13"/>
+      <c r="A13" s="5"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="5"/>
+      <c r="L13" s="5"/>
+      <c r="M13" s="5"/>
+      <c r="N13" s="5"/>
+      <c r="O13" s="5"/>
     </row>
     <row r="14" ht="20.05" customHeight="1">
-      <c r="A14" s="11"/>
-      <c r="B14" s="12"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="13"/>
-      <c r="I14" s="13"/>
-      <c r="J14" s="13"/>
-      <c r="K14" s="13"/>
-      <c r="L14" s="13"/>
-      <c r="M14" s="13"/>
+      <c r="A14" s="5"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5"/>
+      <c r="M14" s="5"/>
+      <c r="N14" s="5"/>
+      <c r="O14" s="5"/>
     </row>
     <row r="15" ht="20.05" customHeight="1">
-      <c r="A15" s="11"/>
-      <c r="B15" s="12"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="13"/>
-      <c r="J15" s="13"/>
-      <c r="K15" s="13"/>
-      <c r="L15" s="13"/>
-      <c r="M15" s="13"/>
+      <c r="A15" s="5"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="5"/>
+      <c r="L15" s="5"/>
+      <c r="M15" s="5"/>
+      <c r="N15" s="5"/>
+      <c r="O15" s="5"/>
     </row>
     <row r="16" ht="20.05" customHeight="1">
-      <c r="A16" s="11"/>
-      <c r="B16" s="12"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="13"/>
-      <c r="G16" s="13"/>
-      <c r="H16" s="13"/>
-      <c r="I16" s="13"/>
-      <c r="J16" s="13"/>
-      <c r="K16" s="13"/>
-      <c r="L16" s="13"/>
-      <c r="M16" s="13"/>
+      <c r="A16" s="5"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="5"/>
+      <c r="N16" s="5"/>
+      <c r="O16" s="5"/>
     </row>
     <row r="17" ht="20.05" customHeight="1">
-      <c r="A17" s="11"/>
-      <c r="B17" s="12"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="13"/>
-      <c r="J17" s="13"/>
-      <c r="K17" s="13"/>
-      <c r="L17" s="13"/>
-      <c r="M17" s="13"/>
+      <c r="A17" s="5"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
+      <c r="K17" s="5"/>
+      <c r="L17" s="5"/>
+      <c r="M17" s="5"/>
+      <c r="N17" s="5"/>
+      <c r="O17" s="5"/>
     </row>
     <row r="18" ht="20.05" customHeight="1">
-      <c r="A18" s="11"/>
-      <c r="B18" s="12"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="13"/>
-      <c r="J18" s="13"/>
-      <c r="K18" s="13"/>
-      <c r="L18" s="13"/>
-      <c r="M18" s="13"/>
+      <c r="A18" s="5"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="5"/>
+      <c r="L18" s="5"/>
+      <c r="M18" s="5"/>
+      <c r="N18" s="5"/>
+      <c r="O18" s="5"/>
     </row>
     <row r="19" ht="20.05" customHeight="1">
-      <c r="A19" s="11"/>
-      <c r="B19" s="12"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="13"/>
-      <c r="I19" s="13"/>
-      <c r="J19" s="13"/>
-      <c r="K19" s="13"/>
-      <c r="L19" s="13"/>
-      <c r="M19" s="13"/>
+      <c r="A19" s="5"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+      <c r="K19" s="5"/>
+      <c r="L19" s="5"/>
+      <c r="M19" s="5"/>
+      <c r="N19" s="5"/>
+      <c r="O19" s="5"/>
     </row>
     <row r="20" ht="20.05" customHeight="1">
-      <c r="A20" s="11"/>
-      <c r="B20" s="12"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="13"/>
-      <c r="I20" s="13"/>
-      <c r="J20" s="13"/>
-      <c r="K20" s="13"/>
-      <c r="L20" s="13"/>
-      <c r="M20" s="13"/>
+      <c r="A20" s="5"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+      <c r="K20" s="5"/>
+      <c r="L20" s="5"/>
+      <c r="M20" s="5"/>
+      <c r="N20" s="5"/>
+      <c r="O20" s="5"/>
     </row>
     <row r="21" ht="20.05" customHeight="1">
-      <c r="A21" s="11"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="13"/>
-      <c r="J21" s="13"/>
-      <c r="K21" s="13"/>
-      <c r="L21" s="13"/>
-      <c r="M21" s="13"/>
+      <c r="A21" s="5"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+      <c r="K21" s="5"/>
+      <c r="L21" s="5"/>
+      <c r="M21" s="5"/>
+      <c r="N21" s="5"/>
+      <c r="O21" s="5"/>
     </row>
     <row r="22" ht="20.05" customHeight="1">
-      <c r="A22" s="11"/>
-      <c r="B22" s="12"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="13"/>
-      <c r="H22" s="13"/>
-      <c r="I22" s="13"/>
-      <c r="J22" s="13"/>
-      <c r="K22" s="13"/>
-      <c r="L22" s="13"/>
-      <c r="M22" s="13"/>
+      <c r="A22" s="5"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
+      <c r="K22" s="5"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="5"/>
+      <c r="N22" s="5"/>
+      <c r="O22" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.277778" footer="0.277778"/>

--- a/mockdata/Epicollect_Metadata.xlsx
+++ b/mockdata/Epicollect_Metadata.xlsx
@@ -1,17 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/taylorlaurensergel/Desktop/Honours 26'/IMY/Project/IMY772Project/mockdata/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04A903ED-1FED-1D41-8BF8-BCDF27FB5C36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="40" windowWidth="15960" windowHeight="18080"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="172">
   <si>
     <t>Site ID</t>
   </si>
@@ -67,12 +76,6 @@
     <t>Apies River</t>
   </si>
   <si>
-    <t>-25.747</t>
-  </si>
-  <si>
-    <t>28.229</t>
-  </si>
-  <si>
     <t>SAMP-001</t>
   </si>
   <si>
@@ -103,12 +106,6 @@
     <t>Hammanskraal</t>
   </si>
   <si>
-    <t>-25.750</t>
-  </si>
-  <si>
-    <t>28.230</t>
-  </si>
-  <si>
     <t>SAMP-002</t>
   </si>
   <si>
@@ -133,12 +130,6 @@
     <t>Tshwane</t>
   </si>
   <si>
-    <t>-25.752</t>
-  </si>
-  <si>
-    <t>28.231</t>
-  </si>
-  <si>
     <t>SAMP-003</t>
   </si>
   <si>
@@ -158,41 +149,423 @@
   </si>
   <si>
     <t>5.8</t>
+  </si>
+  <si>
+    <t>-25.7479</t>
+  </si>
+  <si>
+    <t>28.2293</t>
+  </si>
+  <si>
+    <t>-25.4712</t>
+  </si>
+  <si>
+    <t>28.2897</t>
+  </si>
+  <si>
+    <t>-25.7312</t>
+  </si>
+  <si>
+    <t>28.2183</t>
+  </si>
+  <si>
+    <t>SAMP-004</t>
+  </si>
+  <si>
+    <t>AP-04-OCT</t>
+  </si>
+  <si>
+    <t>F01</t>
+  </si>
+  <si>
+    <t>East London</t>
+  </si>
+  <si>
+    <t>Buffalo River</t>
+  </si>
+  <si>
+    <t>SAMP-005</t>
+  </si>
+  <si>
+    <t>BU-05-MAY</t>
+  </si>
+  <si>
+    <t>SAMP-006</t>
+  </si>
+  <si>
+    <t>BU-06-AUG</t>
+  </si>
+  <si>
+    <t>16S rRNA</t>
+  </si>
+  <si>
+    <t>D12</t>
+  </si>
+  <si>
+    <t>Stellenbosch</t>
+  </si>
+  <si>
+    <t>Eerste River</t>
+  </si>
+  <si>
+    <t>SAMP-007</t>
+  </si>
+  <si>
+    <t>EE-07-JUN</t>
+  </si>
+  <si>
+    <t>Trip 3</t>
+  </si>
+  <si>
+    <t>E05</t>
+  </si>
+  <si>
+    <t>Durban North</t>
+  </si>
+  <si>
+    <t>Umgeni River</t>
+  </si>
+  <si>
+    <t>SAMP-008</t>
+  </si>
+  <si>
+    <t>UM-08-MAY</t>
+  </si>
+  <si>
+    <t>SAMP-009</t>
+  </si>
+  <si>
+    <t>UM-09-OCT</t>
+  </si>
+  <si>
+    <t>SAMP-010</t>
+  </si>
+  <si>
+    <t>AP-10-JUL</t>
+  </si>
+  <si>
+    <t>Trip 4</t>
+  </si>
+  <si>
+    <t>D10</t>
+  </si>
+  <si>
+    <t>Cape Town Bellville</t>
+  </si>
+  <si>
+    <t>Kuils River</t>
+  </si>
+  <si>
+    <t>SAMP-011</t>
+  </si>
+  <si>
+    <t>KU-11-SEP</t>
+  </si>
+  <si>
+    <t>C03</t>
+  </si>
+  <si>
+    <t>Meyerton</t>
+  </si>
+  <si>
+    <t>Vaal River</t>
+  </si>
+  <si>
+    <t>SAMP-012</t>
+  </si>
+  <si>
+    <t>VA-12-MAY</t>
+  </si>
+  <si>
+    <t>SAMP-013</t>
+  </si>
+  <si>
+    <t>EE-13-OCT</t>
+  </si>
+  <si>
+    <t>SAMP-014</t>
+  </si>
+  <si>
+    <t>VA-14-OCT</t>
+  </si>
+  <si>
+    <t>SAMP-015</t>
+  </si>
+  <si>
+    <t>AP-15-MAY</t>
+  </si>
+  <si>
+    <t>E06</t>
+  </si>
+  <si>
+    <t>Pinetown</t>
+  </si>
+  <si>
+    <t>Umhlatuzana</t>
+  </si>
+  <si>
+    <t>SAMP-016</t>
+  </si>
+  <si>
+    <t>UM-16-SEP</t>
+  </si>
+  <si>
+    <t>SAMP-017</t>
+  </si>
+  <si>
+    <t>AP-17-OCT</t>
+  </si>
+  <si>
+    <t>SAMP-018</t>
+  </si>
+  <si>
+    <t>KU-18-SEP</t>
+  </si>
+  <si>
+    <t>SAMP-019</t>
+  </si>
+  <si>
+    <t>AP-19-JUN</t>
+  </si>
+  <si>
+    <t>SAMP-020</t>
+  </si>
+  <si>
+    <t>AP-20-MAY</t>
+  </si>
+  <si>
+    <t>A12</t>
+  </si>
+  <si>
+    <t>Onderstepoort</t>
+  </si>
+  <si>
+    <t>SAMP-021</t>
+  </si>
+  <si>
+    <t>AP-21-OCT</t>
+  </si>
+  <si>
+    <t>SAMP-022</t>
+  </si>
+  <si>
+    <t>EE-22-MAY</t>
+  </si>
+  <si>
+    <t>C02</t>
+  </si>
+  <si>
+    <t>Vereeniging</t>
+  </si>
+  <si>
+    <t>SAMP-023</t>
+  </si>
+  <si>
+    <t>VA-23-MAY</t>
+  </si>
+  <si>
+    <t>SAMP-024</t>
+  </si>
+  <si>
+    <t>VA-24-MAY</t>
+  </si>
+  <si>
+    <t>SAMP-025</t>
+  </si>
+  <si>
+    <t>VA-25-OCT</t>
+  </si>
+  <si>
+    <t>SAMP-026</t>
+  </si>
+  <si>
+    <t>AP-26-AUG</t>
+  </si>
+  <si>
+    <t>SAMP-027</t>
+  </si>
+  <si>
+    <t>VA-27-DEC</t>
+  </si>
+  <si>
+    <t>SAMP-028</t>
+  </si>
+  <si>
+    <t>AP-28-JUL</t>
+  </si>
+  <si>
+    <t>Pretoria CBD</t>
+  </si>
+  <si>
+    <t>SAMP-029</t>
+  </si>
+  <si>
+    <t>AP-29-NOV</t>
+  </si>
+  <si>
+    <t>F02</t>
+  </si>
+  <si>
+    <t>Port Elizabeth</t>
+  </si>
+  <si>
+    <t>Swartkops River</t>
+  </si>
+  <si>
+    <t>SAMP-030</t>
+  </si>
+  <si>
+    <t>SW-30-JUL</t>
+  </si>
+  <si>
+    <t>SAMP-031</t>
+  </si>
+  <si>
+    <t>AP-31-DEC</t>
+  </si>
+  <si>
+    <t>SAMP-032</t>
+  </si>
+  <si>
+    <t>VA-32-DEC</t>
+  </si>
+  <si>
+    <t>SAMP-033</t>
+  </si>
+  <si>
+    <t>UM-33-JUN</t>
+  </si>
+  <si>
+    <t>SAMP-034</t>
+  </si>
+  <si>
+    <t>KU-34-SEP</t>
+  </si>
+  <si>
+    <t>D11</t>
+  </si>
+  <si>
+    <t>Paarl</t>
+  </si>
+  <si>
+    <t>Berg River</t>
+  </si>
+  <si>
+    <t>SAMP-035</t>
+  </si>
+  <si>
+    <t>BE-35-DEC</t>
+  </si>
+  <si>
+    <t>SAMP-036</t>
+  </si>
+  <si>
+    <t>VA-36-JUL</t>
+  </si>
+  <si>
+    <t>SAMP-037</t>
+  </si>
+  <si>
+    <t>SW-37-SEP</t>
+  </si>
+  <si>
+    <t>C01</t>
+  </si>
+  <si>
+    <t>Johannesburg South</t>
+  </si>
+  <si>
+    <t>Klip River</t>
+  </si>
+  <si>
+    <t>SAMP-038</t>
+  </si>
+  <si>
+    <t>KL-38-AUG</t>
+  </si>
+  <si>
+    <t>SAMP-039</t>
+  </si>
+  <si>
+    <t>AP-39-DEC</t>
+  </si>
+  <si>
+    <t>A11</t>
+  </si>
+  <si>
+    <t>Silverton</t>
+  </si>
+  <si>
+    <t>SAMP-040</t>
+  </si>
+  <si>
+    <t>AP-40-OCT</t>
+  </si>
+  <si>
+    <t>SAMP-041</t>
+  </si>
+  <si>
+    <t>KL-41-AUG</t>
+  </si>
+  <si>
+    <t>SAMP-042</t>
+  </si>
+  <si>
+    <t>BU-42-MAY</t>
+  </si>
+  <si>
+    <t>SAMP-043</t>
+  </si>
+  <si>
+    <t>VA-43-AUG</t>
+  </si>
+  <si>
+    <t>SAMP-044</t>
+  </si>
+  <si>
+    <t>UM-44-JUL</t>
+  </si>
+  <si>
+    <t>SAMP-045</t>
+  </si>
+  <si>
+    <t>BE-45-JUL</t>
+  </si>
+  <si>
+    <t>SAMP-046</t>
+  </si>
+  <si>
+    <t>SW-46-MAY</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="0" formatCode="General"/>
-  </numFmts>
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color indexed="8"/>
       <name val="Helvetica Neue"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color indexed="8"/>
-      <name val="Helvetica Neue"/>
-    </font>
-    <font>
-      <sz val="15"/>
-      <color indexed="8"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b val="1"/>
+      <b/>
       <sz val="12"/>
       <color indexed="9"/>
       <name val="Helvetica"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color indexed="9"/>
       <name val="Helvetica"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color indexed="8"/>
+      <name val="Helvetica"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -234,28 +607,37 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+  <cellXfs count="9">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -265,25 +647,85 @@
   <tableStyles count="0"/>
   <colors>
     <indexedColors>
-      <rgbColor rgb="ff000000"/>
-      <rgbColor rgb="ffffffff"/>
-      <rgbColor rgb="ffff0000"/>
-      <rgbColor rgb="ff00ff00"/>
-      <rgbColor rgb="ff0000ff"/>
-      <rgbColor rgb="ffffff00"/>
-      <rgbColor rgb="ffff00ff"/>
-      <rgbColor rgb="ff00ffff"/>
-      <rgbColor rgb="ff000000"/>
-      <rgbColor rgb="ff1f1f1f"/>
-      <rgbColor rgb="ffefefef"/>
-      <rgbColor rgb="ffa5a5a5"/>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FF1F1F1F"/>
+      <rgbColor rgb="FFEFEFEF"/>
+      <rgbColor rgb="FFA5A5A5"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Blank">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Blank">
   <a:themeElements>
     <a:clrScheme name="Blank">
       <a:dk1>
@@ -485,7 +927,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="50800" tIns="50800" rIns="50800" bIns="50800" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="50800" tIns="50800" rIns="50800" bIns="50800" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -503,7 +945,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1100" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1100" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -532,7 +974,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -557,7 +999,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -582,7 +1024,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -607,7 +1049,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -632,7 +1074,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -657,7 +1099,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -682,7 +1124,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -707,7 +1149,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -732,7 +1174,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -745,9 +1187,15 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
         <a:fontRef idx="none"/>
       </a:style>
     </a:spDef>
@@ -764,7 +1212,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="91439" tIns="45719" rIns="91439" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="91439" tIns="45719" rIns="91439" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t">
         <a:noAutofit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -782,7 +1230,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -807,7 +1255,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -832,7 +1280,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -857,7 +1305,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -882,7 +1330,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -907,7 +1355,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -932,7 +1380,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -957,7 +1405,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -982,7 +1430,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1007,7 +1455,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1020,9 +1468,15 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
         <a:fontRef idx="none"/>
       </a:style>
     </a:lnDef>
@@ -1036,7 +1490,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="50800" tIns="50800" rIns="50800" bIns="50800" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="50800" tIns="50800" rIns="50800" bIns="50800" numCol="1" spcCol="38100" rtlCol="0" anchor="t">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -1054,7 +1508,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1100" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1100" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1083,7 +1537,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1108,7 +1562,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1133,7 +1587,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1158,7 +1612,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1183,7 +1637,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1208,7 +1662,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1233,7 +1687,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1258,7 +1712,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1283,7 +1737,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1296,108 +1750,115 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
         <a:fontRef idx="none"/>
       </a:style>
     </a:txDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O22"/>
-  <sheetFormatPr defaultColWidth="16.3333" defaultRowHeight="13.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:O48"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="16.33203125" defaultRowHeight="60.25" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="15" width="16.3516" style="1" customWidth="1"/>
-    <col min="16" max="16384" width="16.3516" style="1" customWidth="1"/>
+    <col min="1" max="16" width="16.33203125" style="1" customWidth="1"/>
+    <col min="17" max="16384" width="16.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="60.55" customHeight="1">
-      <c r="A1" t="s" s="2">
+    <row r="1" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s" s="2">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s" s="2">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s" s="2">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s" s="2">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s" s="2">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s" s="2">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s" s="2">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s" s="2">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s" s="2">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s" s="2">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s" s="2">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s" s="2">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s" s="2">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s" s="2">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" ht="74.55" customHeight="1">
-      <c r="A2" t="s" s="3">
+    <row r="2" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B2" t="s" s="3">
+      <c r="B2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C2" t="s" s="3">
+      <c r="C2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D2" t="s" s="3">
+      <c r="D2" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E2" t="s" s="3">
+      <c r="G2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F2" t="s" s="3">
+      <c r="H2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G2" t="s" s="3">
+      <c r="I2" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H2" t="s" s="3">
+      <c r="J2" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="I2" t="s" s="3">
+      <c r="K2" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="J2" t="s" s="3">
+      <c r="L2" s="5" t="s">
         <v>24</v>
-      </c>
-      <c r="K2" t="s" s="3">
-        <v>25</v>
-      </c>
-      <c r="L2" t="s" s="3">
-        <v>26</v>
       </c>
       <c r="M2" s="4">
         <v>250</v>
@@ -1405,46 +1866,46 @@
       <c r="N2" s="4">
         <v>400</v>
       </c>
-      <c r="O2" t="s" s="3">
+      <c r="O2" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="3" ht="46.35" customHeight="1">
-      <c r="A3" t="s" s="3">
+      <c r="C3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B3" t="s" s="3">
+      <c r="G3" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C3" t="s" s="3">
-        <v>17</v>
-      </c>
-      <c r="D3" t="s" s="3">
+      <c r="H3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E3" t="s" s="3">
+      <c r="I3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K3" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="F3" t="s" s="3">
+      <c r="L3" s="5" t="s">
         <v>32</v>
-      </c>
-      <c r="G3" t="s" s="3">
-        <v>33</v>
-      </c>
-      <c r="H3" t="s" s="3">
-        <v>34</v>
-      </c>
-      <c r="I3" t="s" s="3">
-        <v>23</v>
-      </c>
-      <c r="J3" t="s" s="3">
-        <v>24</v>
-      </c>
-      <c r="K3" t="s" s="3">
-        <v>35</v>
-      </c>
-      <c r="L3" t="s" s="3">
-        <v>36</v>
       </c>
       <c r="M3" s="4">
         <v>260</v>
@@ -1452,46 +1913,46 @@
       <c r="N3" s="4">
         <v>410</v>
       </c>
-      <c r="O3" t="s" s="3">
+      <c r="O3" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="4" ht="60.35" customHeight="1">
-      <c r="A4" t="s" s="3">
+      <c r="H4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B4" t="s" s="3">
+      <c r="J4" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C4" t="s" s="3">
-        <v>17</v>
-      </c>
-      <c r="D4" t="s" s="3">
+      <c r="K4" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="E4" t="s" s="3">
+      <c r="L4" s="5" t="s">
         <v>41</v>
-      </c>
-      <c r="F4" t="s" s="3">
-        <v>42</v>
-      </c>
-      <c r="G4" t="s" s="3">
-        <v>43</v>
-      </c>
-      <c r="H4" t="s" s="3">
-        <v>34</v>
-      </c>
-      <c r="I4" t="s" s="3">
-        <v>44</v>
-      </c>
-      <c r="J4" t="s" s="3">
-        <v>45</v>
-      </c>
-      <c r="K4" t="s" s="3">
-        <v>46</v>
-      </c>
-      <c r="L4" t="s" s="3">
-        <v>47</v>
       </c>
       <c r="M4" s="4">
         <v>280</v>
@@ -1499,319 +1960,2051 @@
       <c r="N4" s="4">
         <v>450</v>
       </c>
-      <c r="O4" t="s" s="3">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" ht="46.35" customHeight="1">
-      <c r="A5" s="5"/>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
-      <c r="N5" s="5"/>
-      <c r="O5" s="5"/>
-    </row>
-    <row r="6" ht="20.05" customHeight="1">
-      <c r="A6" s="5"/>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="5"/>
-      <c r="O6" s="5"/>
-    </row>
-    <row r="7" ht="20.05" customHeight="1">
-      <c r="A7" s="5"/>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5"/>
-      <c r="M7" s="5"/>
-      <c r="N7" s="5"/>
-      <c r="O7" s="5"/>
-    </row>
-    <row r="8" ht="20.05" customHeight="1">
-      <c r="A8" s="5"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5"/>
-      <c r="M8" s="5"/>
-      <c r="N8" s="5"/>
-      <c r="O8" s="5"/>
-    </row>
-    <row r="9" ht="20.05" customHeight="1">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
-      <c r="L9" s="5"/>
-      <c r="M9" s="5"/>
-      <c r="N9" s="5"/>
-      <c r="O9" s="5"/>
-    </row>
-    <row r="10" ht="20.05" customHeight="1">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5"/>
-      <c r="L10" s="5"/>
-      <c r="M10" s="5"/>
-      <c r="N10" s="5"/>
-      <c r="O10" s="5"/>
-    </row>
-    <row r="11" ht="20.05" customHeight="1">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="5"/>
-      <c r="L11" s="5"/>
-      <c r="M11" s="5"/>
-      <c r="N11" s="5"/>
-      <c r="O11" s="5"/>
-    </row>
-    <row r="12" ht="20.05" customHeight="1">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="5"/>
-      <c r="L12" s="5"/>
-      <c r="M12" s="5"/>
-      <c r="N12" s="5"/>
-      <c r="O12" s="5"/>
-    </row>
-    <row r="13" ht="20.05" customHeight="1">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="5"/>
-      <c r="L13" s="5"/>
-      <c r="M13" s="5"/>
-      <c r="N13" s="5"/>
-      <c r="O13" s="5"/>
-    </row>
-    <row r="14" ht="20.05" customHeight="1">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="5"/>
-      <c r="L14" s="5"/>
-      <c r="M14" s="5"/>
-      <c r="N14" s="5"/>
-      <c r="O14" s="5"/>
-    </row>
-    <row r="15" ht="20.05" customHeight="1">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
-      <c r="K15" s="5"/>
-      <c r="L15" s="5"/>
-      <c r="M15" s="5"/>
-      <c r="N15" s="5"/>
-      <c r="O15" s="5"/>
-    </row>
-    <row r="16" ht="20.05" customHeight="1">
-      <c r="A16" s="5"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
-      <c r="J16" s="5"/>
-      <c r="K16" s="5"/>
-      <c r="L16" s="5"/>
-      <c r="M16" s="5"/>
-      <c r="N16" s="5"/>
-      <c r="O16" s="5"/>
-    </row>
-    <row r="17" ht="20.05" customHeight="1">
-      <c r="A17" s="5"/>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-      <c r="I17" s="5"/>
-      <c r="J17" s="5"/>
-      <c r="K17" s="5"/>
-      <c r="L17" s="5"/>
-      <c r="M17" s="5"/>
-      <c r="N17" s="5"/>
-      <c r="O17" s="5"/>
-    </row>
-    <row r="18" ht="20.05" customHeight="1">
-      <c r="A18" s="5"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5"/>
-      <c r="I18" s="5"/>
-      <c r="J18" s="5"/>
-      <c r="K18" s="5"/>
-      <c r="L18" s="5"/>
-      <c r="M18" s="5"/>
-      <c r="N18" s="5"/>
-      <c r="O18" s="5"/>
-    </row>
-    <row r="19" ht="20.05" customHeight="1">
-      <c r="A19" s="5"/>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
-      <c r="I19" s="5"/>
-      <c r="J19" s="5"/>
-      <c r="K19" s="5"/>
-      <c r="L19" s="5"/>
-      <c r="M19" s="5"/>
-      <c r="N19" s="5"/>
-      <c r="O19" s="5"/>
-    </row>
-    <row r="20" ht="20.05" customHeight="1">
-      <c r="A20" s="5"/>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-      <c r="H20" s="5"/>
-      <c r="I20" s="5"/>
-      <c r="J20" s="5"/>
-      <c r="K20" s="5"/>
-      <c r="L20" s="5"/>
-      <c r="M20" s="5"/>
-      <c r="N20" s="5"/>
-      <c r="O20" s="5"/>
-    </row>
-    <row r="21" ht="20.05" customHeight="1">
-      <c r="A21" s="5"/>
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
-      <c r="I21" s="5"/>
-      <c r="J21" s="5"/>
-      <c r="K21" s="5"/>
-      <c r="L21" s="5"/>
-      <c r="M21" s="5"/>
-      <c r="N21" s="5"/>
-      <c r="O21" s="5"/>
-    </row>
-    <row r="22" ht="20.05" customHeight="1">
-      <c r="A22" s="5"/>
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-      <c r="H22" s="5"/>
-      <c r="I22" s="5"/>
-      <c r="J22" s="5"/>
-      <c r="K22" s="5"/>
-      <c r="L22" s="5"/>
-      <c r="M22" s="5"/>
-      <c r="N22" s="5"/>
-      <c r="O22" s="5"/>
+      <c r="O4" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="5">
+        <v>-25.4712</v>
+      </c>
+      <c r="E5" s="5">
+        <v>28.2897</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J5" s="6">
+        <v>45948</v>
+      </c>
+      <c r="K5" s="5">
+        <v>15.2</v>
+      </c>
+      <c r="L5" s="5">
+        <v>6.7</v>
+      </c>
+      <c r="M5" s="5">
+        <v>206</v>
+      </c>
+      <c r="N5" s="5">
+        <v>579</v>
+      </c>
+      <c r="O5" s="5">
+        <v>4.4000000000000004</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" s="5">
+        <v>-32.982999999999997</v>
+      </c>
+      <c r="E6" s="5">
+        <v>27.876899999999999</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J6" s="6">
+        <v>45787</v>
+      </c>
+      <c r="K6" s="5">
+        <v>14.8</v>
+      </c>
+      <c r="L6" s="5">
+        <v>7.4</v>
+      </c>
+      <c r="M6" s="5">
+        <v>186</v>
+      </c>
+      <c r="N6" s="5">
+        <v>587</v>
+      </c>
+      <c r="O6" s="5">
+        <v>4.9000000000000004</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D7" s="5">
+        <v>-32.982999999999997</v>
+      </c>
+      <c r="E7" s="5">
+        <v>27.876899999999999</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J7" s="6">
+        <v>45889</v>
+      </c>
+      <c r="K7" s="5">
+        <v>15.6</v>
+      </c>
+      <c r="L7" s="5">
+        <v>8</v>
+      </c>
+      <c r="M7" s="5">
+        <v>374</v>
+      </c>
+      <c r="N7" s="5">
+        <v>381</v>
+      </c>
+      <c r="O7" s="5">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D8" s="5">
+        <v>-33.932099999999998</v>
+      </c>
+      <c r="E8" s="5">
+        <v>18.860099999999999</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="J8" s="6">
+        <v>45820</v>
+      </c>
+      <c r="K8" s="5">
+        <v>24.4</v>
+      </c>
+      <c r="L8" s="5">
+        <v>7.1</v>
+      </c>
+      <c r="M8" s="5">
+        <v>203</v>
+      </c>
+      <c r="N8" s="5">
+        <v>494</v>
+      </c>
+      <c r="O8" s="5">
+        <v>4.4000000000000004</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D9" s="5">
+        <v>-29.7927</v>
+      </c>
+      <c r="E9" s="5">
+        <v>31.037199999999999</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="J9" s="6">
+        <v>45787</v>
+      </c>
+      <c r="K9" s="5">
+        <v>19</v>
+      </c>
+      <c r="L9" s="5">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="M9" s="5">
+        <v>276</v>
+      </c>
+      <c r="N9" s="5">
+        <v>340</v>
+      </c>
+      <c r="O9" s="5">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D10" s="5">
+        <v>-29.7927</v>
+      </c>
+      <c r="E10" s="5">
+        <v>31.037199999999999</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J10" s="6">
+        <v>45948</v>
+      </c>
+      <c r="K10" s="5">
+        <v>12.6</v>
+      </c>
+      <c r="L10" s="5">
+        <v>6.9</v>
+      </c>
+      <c r="M10" s="5">
+        <v>254</v>
+      </c>
+      <c r="N10" s="5">
+        <v>340</v>
+      </c>
+      <c r="O10" s="5">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" s="5">
+        <v>-25.4712</v>
+      </c>
+      <c r="E11" s="5">
+        <v>28.2897</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="J11" s="6">
+        <v>45853</v>
+      </c>
+      <c r="K11" s="5">
+        <v>20.3</v>
+      </c>
+      <c r="L11" s="5">
+        <v>7.1</v>
+      </c>
+      <c r="M11" s="5">
+        <v>274</v>
+      </c>
+      <c r="N11" s="5">
+        <v>481</v>
+      </c>
+      <c r="O11" s="5">
+        <v>4.9000000000000004</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D12" s="5">
+        <v>-33.900100000000002</v>
+      </c>
+      <c r="E12" s="5">
+        <v>18.632999999999999</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J12" s="6">
+        <v>45905</v>
+      </c>
+      <c r="K12" s="5">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="L12" s="5">
+        <v>6.9</v>
+      </c>
+      <c r="M12" s="5">
+        <v>298</v>
+      </c>
+      <c r="N12" s="5">
+        <v>494</v>
+      </c>
+      <c r="O12" s="5">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D13" s="5">
+        <v>-26.556899999999999</v>
+      </c>
+      <c r="E13" s="5">
+        <v>28.013200000000001</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="J13" s="6">
+        <v>45787</v>
+      </c>
+      <c r="K13" s="5">
+        <v>22.7</v>
+      </c>
+      <c r="L13" s="5">
+        <v>7.9</v>
+      </c>
+      <c r="M13" s="5">
+        <v>282</v>
+      </c>
+      <c r="N13" s="5">
+        <v>437</v>
+      </c>
+      <c r="O13" s="5">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D14" s="5">
+        <v>-33.932099999999998</v>
+      </c>
+      <c r="E14" s="5">
+        <v>18.860099999999999</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J14" s="6">
+        <v>45948</v>
+      </c>
+      <c r="K14" s="5">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="L14" s="5">
+        <v>8.1</v>
+      </c>
+      <c r="M14" s="5">
+        <v>297</v>
+      </c>
+      <c r="N14" s="5">
+        <v>373</v>
+      </c>
+      <c r="O14" s="5">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D15" s="5">
+        <v>-26.556899999999999</v>
+      </c>
+      <c r="E15" s="5">
+        <v>28.013200000000001</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="J15" s="6">
+        <v>45948</v>
+      </c>
+      <c r="K15" s="5">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="L15" s="5">
+        <v>7.5</v>
+      </c>
+      <c r="M15" s="5">
+        <v>272</v>
+      </c>
+      <c r="N15" s="5">
+        <v>412</v>
+      </c>
+      <c r="O15" s="5">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-25.731200000000001</v>
+      </c>
+      <c r="E16" s="5">
+        <v>28.218299999999999</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="J16" s="6">
+        <v>45787</v>
+      </c>
+      <c r="K16" s="5">
+        <v>23.2</v>
+      </c>
+      <c r="L16" s="5">
+        <v>6.8</v>
+      </c>
+      <c r="M16" s="5">
+        <v>220</v>
+      </c>
+      <c r="N16" s="5">
+        <v>516</v>
+      </c>
+      <c r="O16" s="5">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-29.826699999999999</v>
+      </c>
+      <c r="E17" s="5">
+        <v>30.8582</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="J17" s="6">
+        <v>45905</v>
+      </c>
+      <c r="K17" s="5">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="L17" s="5">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="M17" s="5">
+        <v>400</v>
+      </c>
+      <c r="N17" s="5">
+        <v>305</v>
+      </c>
+      <c r="O17" s="5">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-25.4712</v>
+      </c>
+      <c r="E18" s="5">
+        <v>28.2897</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="J18" s="6">
+        <v>45948</v>
+      </c>
+      <c r="K18" s="5">
+        <v>13.5</v>
+      </c>
+      <c r="L18" s="5">
+        <v>7.2</v>
+      </c>
+      <c r="M18" s="5">
+        <v>296</v>
+      </c>
+      <c r="N18" s="5">
+        <v>301</v>
+      </c>
+      <c r="O18" s="5">
+        <v>8.3000000000000007</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-33.900100000000002</v>
+      </c>
+      <c r="E19" s="5">
+        <v>18.632999999999999</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J19" s="6">
+        <v>45905</v>
+      </c>
+      <c r="K19" s="5">
+        <v>23.3</v>
+      </c>
+      <c r="L19" s="5">
+        <v>7</v>
+      </c>
+      <c r="M19" s="5">
+        <v>343</v>
+      </c>
+      <c r="N19" s="5">
+        <v>559</v>
+      </c>
+      <c r="O19" s="5">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-25.731200000000001</v>
+      </c>
+      <c r="E20" s="5">
+        <v>28.218299999999999</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="J20" s="6">
+        <v>45820</v>
+      </c>
+      <c r="K20" s="5">
+        <v>24.4</v>
+      </c>
+      <c r="L20" s="5">
+        <v>8.1</v>
+      </c>
+      <c r="M20" s="5">
+        <v>415</v>
+      </c>
+      <c r="N20" s="5">
+        <v>300</v>
+      </c>
+      <c r="O20" s="5">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-25.747900000000001</v>
+      </c>
+      <c r="E21" s="5">
+        <v>28.229299999999999</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J21" s="6">
+        <v>45787</v>
+      </c>
+      <c r="K21" s="5">
+        <v>23.4</v>
+      </c>
+      <c r="L21" s="5">
+        <v>7.9</v>
+      </c>
+      <c r="M21" s="5">
+        <v>258</v>
+      </c>
+      <c r="N21" s="5">
+        <v>422</v>
+      </c>
+      <c r="O21" s="5">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D22" s="5">
+        <v>-25.6478</v>
+      </c>
+      <c r="E22" s="5">
+        <v>28.186399999999999</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J22" s="6">
+        <v>45948</v>
+      </c>
+      <c r="K22" s="5">
+        <v>22.6</v>
+      </c>
+      <c r="L22" s="5">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="M22" s="5">
+        <v>316</v>
+      </c>
+      <c r="N22" s="5">
+        <v>364</v>
+      </c>
+      <c r="O22" s="5">
+        <v>4.5999999999999996</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="D23" s="7">
+        <v>-33.932099999999998</v>
+      </c>
+      <c r="E23" s="7">
+        <v>18.860099999999999</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I23" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J23" s="8">
+        <v>45787</v>
+      </c>
+      <c r="K23" s="7">
+        <v>21.6</v>
+      </c>
+      <c r="L23" s="7">
+        <v>7.7</v>
+      </c>
+      <c r="M23" s="7">
+        <v>408</v>
+      </c>
+      <c r="N23" s="7">
+        <v>579</v>
+      </c>
+      <c r="O23" s="7">
+        <v>4.4000000000000004</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D24" s="7">
+        <v>-26.6752</v>
+      </c>
+      <c r="E24" s="7">
+        <v>27.9285</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="I24" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J24" s="8">
+        <v>45787</v>
+      </c>
+      <c r="K24" s="7">
+        <v>12.3</v>
+      </c>
+      <c r="L24" s="7">
+        <v>6.8</v>
+      </c>
+      <c r="M24" s="7">
+        <v>346</v>
+      </c>
+      <c r="N24" s="7">
+        <v>579</v>
+      </c>
+      <c r="O24" s="7">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D25" s="7">
+        <v>-26.556899999999999</v>
+      </c>
+      <c r="E25" s="7">
+        <v>28.013200000000001</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="I25" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="J25" s="8">
+        <v>45787</v>
+      </c>
+      <c r="K25" s="7">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="L25" s="7">
+        <v>6.8</v>
+      </c>
+      <c r="M25" s="7">
+        <v>375</v>
+      </c>
+      <c r="N25" s="7">
+        <v>472</v>
+      </c>
+      <c r="O25" s="7">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D26" s="7">
+        <v>-26.6752</v>
+      </c>
+      <c r="E26" s="7">
+        <v>27.9285</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="I26" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J26" s="8">
+        <v>45948</v>
+      </c>
+      <c r="K26" s="7">
+        <v>21.5</v>
+      </c>
+      <c r="L26" s="7">
+        <v>7.4</v>
+      </c>
+      <c r="M26" s="7">
+        <v>416</v>
+      </c>
+      <c r="N26" s="7">
+        <v>493</v>
+      </c>
+      <c r="O26" s="7">
+        <v>4.4000000000000004</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D27" s="7">
+        <v>-25.731200000000001</v>
+      </c>
+      <c r="E27" s="7">
+        <v>28.218299999999999</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="H27" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I27" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="J27" s="8">
+        <v>45889</v>
+      </c>
+      <c r="K27" s="7">
+        <v>22</v>
+      </c>
+      <c r="L27" s="7">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="M27" s="7">
+        <v>398</v>
+      </c>
+      <c r="N27" s="7">
+        <v>419</v>
+      </c>
+      <c r="O27" s="7">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A28" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D28" s="7">
+        <v>-26.6752</v>
+      </c>
+      <c r="E28" s="7">
+        <v>27.9285</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="G28" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="H28" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="I28" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="J28" s="8">
+        <v>45627</v>
+      </c>
+      <c r="K28" s="7">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="L28" s="7">
+        <v>7.6</v>
+      </c>
+      <c r="M28" s="7">
+        <v>359</v>
+      </c>
+      <c r="N28" s="7">
+        <v>336</v>
+      </c>
+      <c r="O28" s="7">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A29" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D29" s="7">
+        <v>-25.6478</v>
+      </c>
+      <c r="E29" s="7">
+        <v>28.186399999999999</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="H29" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="I29" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="J29" s="8">
+        <v>45853</v>
+      </c>
+      <c r="K29" s="7">
+        <v>14.9</v>
+      </c>
+      <c r="L29" s="7">
+        <v>7.1</v>
+      </c>
+      <c r="M29" s="7">
+        <v>376</v>
+      </c>
+      <c r="N29" s="7">
+        <v>328</v>
+      </c>
+      <c r="O29" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A30" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D30" s="7">
+        <v>-25.747900000000001</v>
+      </c>
+      <c r="E30" s="7">
+        <v>28.229299999999999</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="G30" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="H30" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="I30" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="J30" s="8">
+        <v>45983</v>
+      </c>
+      <c r="K30" s="7">
+        <v>23.4</v>
+      </c>
+      <c r="L30" s="7">
+        <v>7</v>
+      </c>
+      <c r="M30" s="7">
+        <v>347</v>
+      </c>
+      <c r="N30" s="7">
+        <v>555</v>
+      </c>
+      <c r="O30" s="7">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A31" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="D31" s="7">
+        <v>-33.8568</v>
+      </c>
+      <c r="E31" s="7">
+        <v>25.6</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="G31" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="H31" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="I31" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="J31" s="8">
+        <v>45853</v>
+      </c>
+      <c r="K31" s="7">
+        <v>19</v>
+      </c>
+      <c r="L31" s="7">
+        <v>7.8</v>
+      </c>
+      <c r="M31" s="7">
+        <v>289</v>
+      </c>
+      <c r="N31" s="7">
+        <v>598</v>
+      </c>
+      <c r="O31" s="7">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A32" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D32" s="7">
+        <v>-25.4712</v>
+      </c>
+      <c r="E32" s="7">
+        <v>28.2897</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="G32" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="H32" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="I32" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="J32" s="8">
+        <v>45627</v>
+      </c>
+      <c r="K32" s="7">
+        <v>14</v>
+      </c>
+      <c r="L32" s="7">
+        <v>6.8</v>
+      </c>
+      <c r="M32" s="7">
+        <v>354</v>
+      </c>
+      <c r="N32" s="7">
+        <v>516</v>
+      </c>
+      <c r="O32" s="7">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A33" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D33" s="7">
+        <v>-26.6752</v>
+      </c>
+      <c r="E33" s="7">
+        <v>27.9285</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="G33" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="H33" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="I33" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="J33" s="8">
+        <v>45627</v>
+      </c>
+      <c r="K33" s="7">
+        <v>20.8</v>
+      </c>
+      <c r="L33" s="7">
+        <v>6.7</v>
+      </c>
+      <c r="M33" s="7">
+        <v>406</v>
+      </c>
+      <c r="N33" s="7">
+        <v>574</v>
+      </c>
+      <c r="O33" s="7">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A34" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="D34" s="7">
+        <v>-29.826699999999999</v>
+      </c>
+      <c r="E34" s="7">
+        <v>30.8582</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="G34" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="H34" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="I34" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="J34" s="8">
+        <v>45820</v>
+      </c>
+      <c r="K34" s="7">
+        <v>24.4</v>
+      </c>
+      <c r="L34" s="7">
+        <v>8</v>
+      </c>
+      <c r="M34" s="7">
+        <v>247</v>
+      </c>
+      <c r="N34" s="7">
+        <v>556</v>
+      </c>
+      <c r="O34" s="7">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A35" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D35" s="7">
+        <v>-33.900100000000002</v>
+      </c>
+      <c r="E35" s="7">
+        <v>18.632999999999999</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="G35" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="H35" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I35" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J35" s="8">
+        <v>45905</v>
+      </c>
+      <c r="K35" s="7">
+        <v>14</v>
+      </c>
+      <c r="L35" s="7">
+        <v>7.8</v>
+      </c>
+      <c r="M35" s="7">
+        <v>318</v>
+      </c>
+      <c r="N35" s="7">
+        <v>571</v>
+      </c>
+      <c r="O35" s="7">
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A36" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="D36" s="7">
+        <v>-33.721699999999998</v>
+      </c>
+      <c r="E36" s="7">
+        <v>18.983000000000001</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="G36" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="H36" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="I36" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="J36" s="8">
+        <v>45627</v>
+      </c>
+      <c r="K36" s="7">
+        <v>15.1</v>
+      </c>
+      <c r="L36" s="7">
+        <v>6.9</v>
+      </c>
+      <c r="M36" s="7">
+        <v>325</v>
+      </c>
+      <c r="N36" s="7">
+        <v>340</v>
+      </c>
+      <c r="O36" s="7">
+        <v>4.4000000000000004</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A37" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D37" s="7">
+        <v>-26.556899999999999</v>
+      </c>
+      <c r="E37" s="7">
+        <v>28.013200000000001</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="G37" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="H37" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="I37" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J37" s="8">
+        <v>45853</v>
+      </c>
+      <c r="K37" s="7">
+        <v>14.1</v>
+      </c>
+      <c r="L37" s="7">
+        <v>7.4</v>
+      </c>
+      <c r="M37" s="7">
+        <v>335</v>
+      </c>
+      <c r="N37" s="7">
+        <v>516</v>
+      </c>
+      <c r="O37" s="7">
+        <v>8.3000000000000007</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A38" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="D38" s="7">
+        <v>-33.8568</v>
+      </c>
+      <c r="E38" s="7">
+        <v>25.6</v>
+      </c>
+      <c r="F38" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G38" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="H38" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="I38" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="J38" s="8">
+        <v>45905</v>
+      </c>
+      <c r="K38" s="7">
+        <v>17.7</v>
+      </c>
+      <c r="L38" s="7">
+        <v>7.4</v>
+      </c>
+      <c r="M38" s="7">
+        <v>210</v>
+      </c>
+      <c r="N38" s="7">
+        <v>426</v>
+      </c>
+      <c r="O38" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A39" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="D39" s="7">
+        <v>-26.3142</v>
+      </c>
+      <c r="E39" s="7">
+        <v>27.9254</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G39" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="H39" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="I39" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J39" s="8">
+        <v>45889</v>
+      </c>
+      <c r="K39" s="7">
+        <v>15</v>
+      </c>
+      <c r="L39" s="7">
+        <v>8</v>
+      </c>
+      <c r="M39" s="7">
+        <v>400</v>
+      </c>
+      <c r="N39" s="7">
+        <v>469</v>
+      </c>
+      <c r="O39" s="7">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A40" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D40" s="7">
+        <v>-25.4712</v>
+      </c>
+      <c r="E40" s="7">
+        <v>28.2897</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="G40" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="H40" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="I40" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="J40" s="8">
+        <v>45627</v>
+      </c>
+      <c r="K40" s="7">
+        <v>19.5</v>
+      </c>
+      <c r="L40" s="7">
+        <v>6.9</v>
+      </c>
+      <c r="M40" s="7">
+        <v>301</v>
+      </c>
+      <c r="N40" s="7">
+        <v>508</v>
+      </c>
+      <c r="O40" s="7">
+        <v>4.9000000000000004</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A41" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D41" s="7">
+        <v>-25.761800000000001</v>
+      </c>
+      <c r="E41" s="7">
+        <v>28.275200000000002</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="G41" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="H41" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="I41" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="J41" s="8">
+        <v>45948</v>
+      </c>
+      <c r="K41" s="7">
+        <v>20.8</v>
+      </c>
+      <c r="L41" s="7">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="M41" s="7">
+        <v>205</v>
+      </c>
+      <c r="N41" s="7">
+        <v>331</v>
+      </c>
+      <c r="O41" s="7">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A42" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="D42" s="7">
+        <v>-26.3142</v>
+      </c>
+      <c r="E42" s="7">
+        <v>27.9254</v>
+      </c>
+      <c r="F42" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="G42" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="H42" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I42" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J42" s="8">
+        <v>45889</v>
+      </c>
+      <c r="K42" s="7">
+        <v>17.5</v>
+      </c>
+      <c r="L42" s="7">
+        <v>7</v>
+      </c>
+      <c r="M42" s="7">
+        <v>243</v>
+      </c>
+      <c r="N42" s="7">
+        <v>338</v>
+      </c>
+      <c r="O42" s="7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A43" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D43" s="7">
+        <v>-32.982999999999997</v>
+      </c>
+      <c r="E43" s="7">
+        <v>27.876899999999999</v>
+      </c>
+      <c r="F43" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="G43" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="H43" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="I43" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J43" s="8">
+        <v>45787</v>
+      </c>
+      <c r="K43" s="7">
+        <v>24.6</v>
+      </c>
+      <c r="L43" s="7">
+        <v>8.1</v>
+      </c>
+      <c r="M43" s="7">
+        <v>397</v>
+      </c>
+      <c r="N43" s="7">
+        <v>421</v>
+      </c>
+      <c r="O43" s="7">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A44" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D44" s="7">
+        <v>-26.556899999999999</v>
+      </c>
+      <c r="E44" s="7">
+        <v>28.013200000000001</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="G44" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="H44" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I44" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="J44" s="8">
+        <v>45889</v>
+      </c>
+      <c r="K44" s="7">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="L44" s="7">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="M44" s="7">
+        <v>247</v>
+      </c>
+      <c r="N44" s="7">
+        <v>532</v>
+      </c>
+      <c r="O44" s="7">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A45" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="D45" s="7">
+        <v>-29.7927</v>
+      </c>
+      <c r="E45" s="7">
+        <v>31.037199999999999</v>
+      </c>
+      <c r="F45" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="G45" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="H45" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="I45" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="J45" s="8">
+        <v>45853</v>
+      </c>
+      <c r="K45" s="7">
+        <v>19.5</v>
+      </c>
+      <c r="L45" s="7">
+        <v>7.4</v>
+      </c>
+      <c r="M45" s="7">
+        <v>371</v>
+      </c>
+      <c r="N45" s="7">
+        <v>460</v>
+      </c>
+      <c r="O45" s="7">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A46" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="D46" s="7">
+        <v>-33.721699999999998</v>
+      </c>
+      <c r="E46" s="7">
+        <v>18.983000000000001</v>
+      </c>
+      <c r="F46" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="G46" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="H46" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I46" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="J46" s="8">
+        <v>45853</v>
+      </c>
+      <c r="K46" s="7">
+        <v>12.9</v>
+      </c>
+      <c r="L46" s="7">
+        <v>6.6</v>
+      </c>
+      <c r="M46" s="7">
+        <v>400</v>
+      </c>
+      <c r="N46" s="7">
+        <v>420</v>
+      </c>
+      <c r="O46" s="7">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A47" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="D47" s="7">
+        <v>-33.8568</v>
+      </c>
+      <c r="E47" s="7">
+        <v>25.6</v>
+      </c>
+      <c r="F47" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="G47" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="H47" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="I47" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="J47" s="8">
+        <v>45787</v>
+      </c>
+      <c r="K47" s="7">
+        <v>19.3</v>
+      </c>
+      <c r="L47" s="7">
+        <v>7</v>
+      </c>
+      <c r="M47" s="7">
+        <v>246</v>
+      </c>
+      <c r="N47" s="7">
+        <v>404</v>
+      </c>
+      <c r="O47" s="7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A48" s="7"/>
+      <c r="B48" s="7"/>
+      <c r="C48" s="7"/>
+      <c r="D48" s="7"/>
+      <c r="E48" s="7"/>
+      <c r="F48" s="7"/>
+      <c r="G48" s="7"/>
+      <c r="H48" s="7"/>
+      <c r="I48" s="7"/>
+      <c r="J48" s="7"/>
+      <c r="K48" s="7"/>
+      <c r="L48" s="7"/>
+      <c r="M48" s="7"/>
+      <c r="N48" s="7"/>
+      <c r="O48" s="7"/>
     </row>
   </sheetData>
-  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.277778" footer="0.277778"/>
-  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="72" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.27777800000000002" footer="0.27777800000000002"/>
+  <pageSetup scale="72" orientation="portrait"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>

--- a/mockdata/Epicollect_Metadata.xlsx
+++ b/mockdata/Epicollect_Metadata.xlsx
@@ -1,203 +1,55 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="40" windowWidth="15960" windowHeight="18080"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="40" windowWidth="15960" windowHeight="18080" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1" sheetId="1" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet 1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="49">
-  <si>
-    <t>Site ID</t>
-  </si>
-  <si>
-    <t>Location Name</t>
-  </si>
-  <si>
-    <t>River Name</t>
-  </si>
-  <si>
-    <t>Lat</t>
-  </si>
-  <si>
-    <t>Lng</t>
-  </si>
-  <si>
-    <t>Sample ID</t>
-  </si>
-  <si>
-    <t>Sample Name</t>
-  </si>
-  <si>
-    <t>Analysis Type</t>
-  </si>
-  <si>
-    <t>Trip ID</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Temp</t>
-  </si>
-  <si>
-    <t>pH</t>
-  </si>
-  <si>
-    <t>TDS</t>
-  </si>
-  <si>
-    <t>EC</t>
-  </si>
-  <si>
-    <t>DO</t>
-  </si>
-  <si>
-    <t>A10</t>
-  </si>
-  <si>
-    <t>Pretoria</t>
-  </si>
-  <si>
-    <t>Apies River</t>
-  </si>
-  <si>
-    <t>-25.747</t>
-  </si>
-  <si>
-    <t>28.229</t>
-  </si>
-  <si>
-    <t>SAMP-001</t>
-  </si>
-  <si>
-    <t>AP-01-MAY</t>
-  </si>
-  <si>
-    <t>Metagenomics</t>
-  </si>
-  <si>
-    <t>Trip 1</t>
-  </si>
-  <si>
-    <t>2025-05-10</t>
-  </si>
-  <si>
-    <t>18.5</t>
-  </si>
-  <si>
-    <t>7.2</t>
-  </si>
-  <si>
-    <t>6.5</t>
-  </si>
-  <si>
-    <t>B26</t>
-  </si>
-  <si>
-    <t>Hammanskraal</t>
-  </si>
-  <si>
-    <t>-25.750</t>
-  </si>
-  <si>
-    <t>28.230</t>
-  </si>
-  <si>
-    <t>SAMP-002</t>
-  </si>
-  <si>
-    <t>AP-02-MAY</t>
-  </si>
-  <si>
-    <t>WGS</t>
-  </si>
-  <si>
-    <t>19.1</t>
-  </si>
-  <si>
-    <t>7.4</t>
-  </si>
-  <si>
-    <t>6.2</t>
-  </si>
-  <si>
-    <t>B27</t>
-  </si>
-  <si>
-    <t>Tshwane</t>
-  </si>
-  <si>
-    <t>-25.752</t>
-  </si>
-  <si>
-    <t>28.231</t>
-  </si>
-  <si>
-    <t>SAMP-003</t>
-  </si>
-  <si>
-    <t>AP-03-JUL</t>
-  </si>
-  <si>
-    <t>Trip 2</t>
-  </si>
-  <si>
-    <t>2025-07-15</t>
-  </si>
-  <si>
-    <t>15.3</t>
-  </si>
-  <si>
-    <t>6.9</t>
-  </si>
-  <si>
-    <t>5.8</t>
-  </si>
-</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="0" formatCode="General"/>
-  </numFmts>
-  <fonts count="5">
+  <numFmts count="0"/>
+  <fonts count="6">
     <font>
+      <name val="Helvetica Neue"/>
+      <color indexed="8"/>
       <sz val="10"/>
-      <color indexed="8"/>
-      <name val="Helvetica Neue"/>
     </font>
     <font>
+      <name val="Helvetica Neue"/>
+      <color indexed="8"/>
       <sz val="12"/>
-      <color indexed="8"/>
-      <name val="Helvetica Neue"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <color indexed="8"/>
       <sz val="15"/>
-      <color indexed="8"/>
-      <name val="Calibri"/>
+    </font>
+    <font>
+      <name val="Helvetica"/>
+      <b val="1"/>
+      <color indexed="9"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Helvetica"/>
+      <color indexed="9"/>
+      <sz val="12"/>
     </font>
     <font>
       <b val="1"/>
-      <sz val="12"/>
-      <color indexed="9"/>
-      <name val="Helvetica"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color indexed="9"/>
-      <name val="Helvetica"/>
+      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -206,6 +58,11 @@
       <patternFill patternType="solid">
         <fgColor indexed="10"/>
         <bgColor auto="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F3864"/>
       </patternFill>
     </fill>
   </fills>
@@ -234,35 +91,38 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+  <cellXfs count="8">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="ff000000"/>
@@ -1307,513 +1167,2986 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O22"/>
-  <sheetFormatPr defaultColWidth="16.3333" defaultRowHeight="13.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O44"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="16.3333" defaultRowHeight="13.9" customHeight="1" outlineLevelRow="0"/>
   <cols>
-    <col min="1" max="15" width="16.3516" style="1" customWidth="1"/>
-    <col min="16" max="16384" width="16.3516" style="1" customWidth="1"/>
+    <col width="16.3516" customWidth="1" style="1" min="1" max="15"/>
+    <col width="16.3516" customWidth="1" style="1" min="16" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="60.55" customHeight="1">
-      <c r="A1" t="s" s="2">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s" s="2">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s" s="2">
+    <row r="1" ht="60.55" customHeight="1" s="6">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Site ID</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>Location Name</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>River Name</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>Lat</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>Lng</t>
+        </is>
+      </c>
+      <c r="F1" s="7" t="inlineStr">
+        <is>
+          <t>Sample ID</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>Sample Name</t>
+        </is>
+      </c>
+      <c r="H1" s="7" t="inlineStr">
+        <is>
+          <t>Analysis Type</t>
+        </is>
+      </c>
+      <c r="I1" s="7" t="inlineStr">
+        <is>
+          <t>Trip ID</t>
+        </is>
+      </c>
+      <c r="J1" s="7" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="K1" s="7" t="inlineStr">
+        <is>
+          <t>Temp</t>
+        </is>
+      </c>
+      <c r="L1" s="7" t="inlineStr">
+        <is>
+          <t>pH</t>
+        </is>
+      </c>
+      <c r="M1" s="7" t="inlineStr">
+        <is>
+          <t>TDS</t>
+        </is>
+      </c>
+      <c r="N1" s="7" t="inlineStr">
+        <is>
+          <t>EC</t>
+        </is>
+      </c>
+      <c r="O1" s="7" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="74.55" customHeight="1" s="6">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>A10</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Pretoria (Upstream)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Apies River</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>-25.6780</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>28.1940</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SAMP-001</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>AR-01-2503</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Metagenomics</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Trip 1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="L2" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="M2" t="n">
+        <v>169</v>
+      </c>
+      <c r="N2" t="n">
+        <v>744</v>
+      </c>
+      <c r="O2" t="n">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="3" ht="46.35" customHeight="1" s="6">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>E16</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Sandton</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Jukskei River</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>-26.0950</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>28.0550</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>SAMP-002</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>JR-02-2503</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>WGS</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Trip 1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="L3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="M3" t="n">
+        <v>509</v>
+      </c>
+      <c r="N3" t="n">
+        <v>365</v>
+      </c>
+      <c r="O3" t="n">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="4" ht="60.35" customHeight="1" s="6">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>B27</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Soshanguve</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Apies River</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>-25.5280</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>28.1010</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>SAMP-003</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>AR-03-2503</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>WGS</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Trip 1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="L4" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="M4" t="n">
+        <v>174</v>
+      </c>
+      <c r="N4" t="n">
+        <v>529</v>
+      </c>
+      <c r="O4" t="n">
         <v>3</v>
       </c>
-      <c r="E1" t="s" s="2">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s" s="2">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s" s="2">
+    </row>
+    <row r="5" ht="46.35" customHeight="1" s="6">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>B26</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Hammanskraal</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Apies River</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>-25.4080</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>28.2710</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SAMP-004</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>AR-04-2503</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Metagenomics</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Trip 1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="L5" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>380</v>
+      </c>
+      <c r="N5" t="n">
+        <v>783</v>
+      </c>
+      <c r="O5" t="n">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="6" ht="20.05" customHeight="1" s="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F03</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Bapsfontein</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Blesbokspruit</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>-26.0750</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>28.3900</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SAMP-005</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>B-05-2503</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Metagenomics</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Trip 1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="L6" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="M6" t="n">
+        <v>469</v>
+      </c>
+      <c r="N6" t="n">
+        <v>424</v>
+      </c>
+      <c r="O6" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="7" ht="20.05" customHeight="1" s="6">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A12</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Pretoria (Downstream)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Apies River</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>-25.8100</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>28.2650</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SAMP-006</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>AR-06-2503</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>WGS</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Trip 1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="L7" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M7" t="n">
+        <v>330</v>
+      </c>
+      <c r="N7" t="n">
+        <v>307</v>
+      </c>
+      <c r="O7" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="8" ht="20.05" customHeight="1" s="6">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>F03</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Bapsfontein</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Blesbokspruit</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>-26.0750</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>28.3900</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SAMP-007</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>B-07-2505</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>WGS</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Trip 2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="L8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="M8" t="n">
+        <v>402</v>
+      </c>
+      <c r="N8" t="n">
+        <v>357</v>
+      </c>
+      <c r="O8" t="n">
+        <v>8.300000000000001</v>
+      </c>
+    </row>
+    <row r="9" ht="20.05" customHeight="1" s="6">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A10</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Pretoria (Upstream)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Apies River</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>-25.6780</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>28.1940</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SAMP-008</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>AR-08-2505</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>WGS</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Trip 2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="L9" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>518</v>
+      </c>
+      <c r="N9" t="n">
+        <v>737</v>
+      </c>
+      <c r="O9" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="10" ht="20.05" customHeight="1" s="6">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>E17</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Lanseria</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Jukskei River</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>-25.9380</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>27.9260</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SAMP-009</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>JR-09-2505</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Metagenomics</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Trip 2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="M10" t="n">
+        <v>236</v>
+      </c>
+      <c r="N10" t="n">
+        <v>782</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="11" ht="20.05" customHeight="1" s="6">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>C01</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Centurion</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Hennops River</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>-25.8610</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>28.1880</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SAMP-010</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>HR-10-2505</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>WGS</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Trip 2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="L11" t="n">
         <v>6</v>
       </c>
-      <c r="H1" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s" s="2">
+      <c r="M11" t="n">
+        <v>197</v>
+      </c>
+      <c r="N11" t="n">
+        <v>838</v>
+      </c>
+      <c r="O11" t="n">
+        <v>10.4</v>
+      </c>
+    </row>
+    <row r="12" ht="20.05" customHeight="1" s="6">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>C02</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Midrand</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Hennops River</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>-25.9940</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>28.1320</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SAMP-011</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>HR-11-2505</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Shotgun</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Trip 2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="L12" t="n">
         <v>8</v>
       </c>
-      <c r="J1" t="s" s="2">
+      <c r="M12" t="n">
+        <v>349</v>
+      </c>
+      <c r="N12" t="n">
+        <v>652</v>
+      </c>
+      <c r="O12" t="n">
+        <v>9.300000000000001</v>
+      </c>
+    </row>
+    <row r="13" ht="20.05" customHeight="1" s="6">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>B27</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Soshanguve</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Apies River</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>-25.5280</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>28.1010</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SAMP-012</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>AR-12-2505</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>WGS</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Trip 2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="L13" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="M13" t="n">
+        <v>580</v>
+      </c>
+      <c r="N13" t="n">
+        <v>159</v>
+      </c>
+      <c r="O13" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="14" ht="20.05" customHeight="1" s="6">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A11</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Pretoria (Midstream)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Apies River</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>-25.7470</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>28.2290</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SAMP-013</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>AR-13-2505</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Metagenomics</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Trip 2</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="L14" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="M14" t="n">
+        <v>208</v>
+      </c>
+      <c r="N14" t="n">
+        <v>271</v>
+      </c>
+      <c r="O14" t="n">
+        <v>8.300000000000001</v>
+      </c>
+    </row>
+    <row r="15" ht="20.05" customHeight="1" s="6">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>E15</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Alexandra</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Jukskei River</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>-26.1050</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>28.0940</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>SAMP-014</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>JR-14-2507</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Metagenomics</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Trip 3</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="L15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="M15" t="n">
+        <v>315</v>
+      </c>
+      <c r="N15" t="n">
+        <v>742</v>
+      </c>
+      <c r="O15" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="16" ht="20.05" customHeight="1" s="6">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>F04</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Benoni</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Blesbokspruit</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>-26.1870</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>28.3200</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>SAMP-015</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>B-15-2507</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Metagenomics</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Trip 3</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="L16" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="M16" t="n">
+        <v>152</v>
+      </c>
+      <c r="N16" t="n">
+        <v>666</v>
+      </c>
+      <c r="O16" t="n">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="17" ht="20.05" customHeight="1" s="6">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>C01</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Centurion</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Hennops River</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>-25.8610</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>28.1880</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SAMP-016</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>HR-16-2507</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Shotgun</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Trip 3</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>15</v>
+      </c>
+      <c r="L17" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="M17" t="n">
+        <v>521</v>
+      </c>
+      <c r="N17" t="n">
+        <v>502</v>
+      </c>
+      <c r="O17" t="n">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="18" ht="20.05" customHeight="1" s="6">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>C03</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kyalami</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Hennops River</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>-26.0220</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>28.0680</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>SAMP-017</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>HR-17-2507</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Metagenomics</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Trip 3</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>16</v>
+      </c>
+      <c r="L18" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M18" t="n">
+        <v>539</v>
+      </c>
+      <c r="N18" t="n">
+        <v>283</v>
+      </c>
+      <c r="O18" t="n">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="19" ht="20.05" customHeight="1" s="6">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>D05</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Hartbeespoort</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Crocodile River</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>-25.7420</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>27.8910</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>SAMP-018</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>CR-18-2507</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Metagenomics</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Trip 3</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="L19" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M19" t="n">
+        <v>95</v>
+      </c>
+      <c r="N19" t="n">
+        <v>235</v>
+      </c>
+      <c r="O19" t="n">
+        <v>10.8</v>
+      </c>
+    </row>
+    <row r="20" ht="20.05" customHeight="1" s="6">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>E16</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Sandton</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Jukskei River</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>-26.0950</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>28.0550</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>SAMP-019</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>JR-19-2507</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Shotgun</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Trip 3</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="L20" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="M20" t="n">
+        <v>140</v>
+      </c>
+      <c r="N20" t="n">
+        <v>308</v>
+      </c>
+      <c r="O20" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="21" ht="20.05" customHeight="1" s="6">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A11</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Pretoria (Midstream)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Apies River</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>-25.7470</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>28.2290</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>SAMP-020</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>AR-20-2507</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>WGS</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Trip 3</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>15</v>
+      </c>
+      <c r="L21" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M21" t="n">
+        <v>139</v>
+      </c>
+      <c r="N21" t="n">
+        <v>733</v>
+      </c>
+      <c r="O21" t="n">
         <v>9</v>
       </c>
-      <c r="K1" t="s" s="2">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s" s="2">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s" s="2">
-        <v>12</v>
-      </c>
-      <c r="N1" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="O1" t="s" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" ht="74.55" customHeight="1">
-      <c r="A2" t="s" s="3">
-        <v>15</v>
-      </c>
-      <c r="B2" t="s" s="3">
-        <v>16</v>
-      </c>
-      <c r="C2" t="s" s="3">
-        <v>17</v>
-      </c>
-      <c r="D2" t="s" s="3">
-        <v>18</v>
-      </c>
-      <c r="E2" t="s" s="3">
-        <v>19</v>
-      </c>
-      <c r="F2" t="s" s="3">
-        <v>20</v>
-      </c>
-      <c r="G2" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="H2" t="s" s="3">
-        <v>22</v>
-      </c>
-      <c r="I2" t="s" s="3">
-        <v>23</v>
-      </c>
-      <c r="J2" t="s" s="3">
+    </row>
+    <row r="22" ht="20.05" customHeight="1" s="6">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>B26</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Hammanskraal</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Apies River</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>-25.4080</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>28.2710</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>SAMP-021</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>AR-21-2507</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Metagenomics</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Trip 3</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="L22" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="M22" t="n">
+        <v>241</v>
+      </c>
+      <c r="N22" t="n">
+        <v>198</v>
+      </c>
+      <c r="O22" t="n">
+        <v>11.1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>F03</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Bapsfontein</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Blesbokspruit</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>-26.0750</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>28.3900</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>SAMP-022</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>B-22-2507</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Metagenomics</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Trip 3</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="L23" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M23" t="n">
+        <v>202</v>
+      </c>
+      <c r="N23" t="n">
+        <v>723</v>
+      </c>
+      <c r="O23" t="n">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>E15</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Alexandra</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Jukskei River</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>-26.1050</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>28.0940</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>SAMP-023</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>JR-23-2509</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>16S rRNA</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Trip 4</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="L24" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="M24" t="n">
+        <v>154</v>
+      </c>
+      <c r="N24" t="n">
+        <v>149</v>
+      </c>
+      <c r="O24" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>E16</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Sandton</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Jukskei River</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>-26.0950</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>28.0550</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>SAMP-024</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>JR-24-2509</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>WGS</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Trip 4</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="L25" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="M25" t="n">
+        <v>389</v>
+      </c>
+      <c r="N25" t="n">
+        <v>766</v>
+      </c>
+      <c r="O25" t="n">
+        <v>11.3</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>C01</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Centurion</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Hennops River</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>-25.8610</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>28.1880</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>SAMP-025</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>HR-25-2509</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>WGS</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Trip 4</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="L26" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="M26" t="n">
+        <v>295</v>
+      </c>
+      <c r="N26" t="n">
+        <v>874</v>
+      </c>
+      <c r="O26" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>B26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Hammanskraal</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Apies River</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>-25.4080</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>28.2710</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>SAMP-026</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>AR-26-2509</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Metagenomics</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Trip 4</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="L27" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="M27" t="n">
+        <v>348</v>
+      </c>
+      <c r="N27" t="n">
+        <v>305</v>
+      </c>
+      <c r="O27" t="n">
+        <v>9.1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>B27</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Soshanguve</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Apies River</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>-25.5280</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>28.1010</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>SAMP-027</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>AR-27-2509</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Metagenomics</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Trip 4</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="L28" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="M28" t="n">
+        <v>231</v>
+      </c>
+      <c r="N28" t="n">
+        <v>580</v>
+      </c>
+      <c r="O28" t="n">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>C02</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Midrand</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Hennops River</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>-25.9940</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>28.1320</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>SAMP-028</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>HR-28-2509</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>16S rRNA</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Trip 4</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="L29" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="M29" t="n">
+        <v>496</v>
+      </c>
+      <c r="N29" t="n">
+        <v>775</v>
+      </c>
+      <c r="O29" t="n">
+        <v>9.1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>A12</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Pretoria (Downstream)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Apies River</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>-25.8100</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>28.2650</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>SAMP-029</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>AR-29-2509</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Metagenomics</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Trip 4</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="L30" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="M30" t="n">
+        <v>501</v>
+      </c>
+      <c r="N30" t="n">
+        <v>961</v>
+      </c>
+      <c r="O30" t="n">
+        <v>8.4</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>F03</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Bapsfontein</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Blesbokspruit</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>-26.0750</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>28.3900</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>SAMP-030</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>B-30-2511</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>WGS</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Trip 5</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="L31" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="M31" t="n">
+        <v>151</v>
+      </c>
+      <c r="N31" t="n">
+        <v>931</v>
+      </c>
+      <c r="O31" t="n">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>C03</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Kyalami</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Hennops River</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>-26.0220</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>28.0680</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>SAMP-031</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>HR-31-2511</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>16S rRNA</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Trip 5</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="L32" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="M32" t="n">
+        <v>433</v>
+      </c>
+      <c r="N32" t="n">
+        <v>886</v>
+      </c>
+      <c r="O32" t="n">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>C01</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Centurion</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Hennops River</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>-25.8610</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>28.1880</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>SAMP-032</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>HR-32-2511</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>16S rRNA</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Trip 5</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="L33" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="M33" t="n">
+        <v>612</v>
+      </c>
+      <c r="N33" t="n">
+        <v>965</v>
+      </c>
+      <c r="O33" t="n">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>B27</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Soshanguve</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Apies River</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>-25.5280</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>28.1010</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>SAMP-033</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>AR-33-2511</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>16S rRNA</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Trip 5</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="L34" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="M34" t="n">
+        <v>414</v>
+      </c>
+      <c r="N34" t="n">
+        <v>552</v>
+      </c>
+      <c r="O34" t="n">
+        <v>8.699999999999999</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>B26</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Hammanskraal</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Apies River</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>-25.4080</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>28.2710</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>SAMP-034</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>AR-34-2511</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Shotgun</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Trip 5</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="L35" t="n">
+        <v>6</v>
+      </c>
+      <c r="M35" t="n">
+        <v>373</v>
+      </c>
+      <c r="N35" t="n">
+        <v>355</v>
+      </c>
+      <c r="O35" t="n">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>E15</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Alexandra</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Jukskei River</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>-26.1050</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>28.0940</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>SAMP-035</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>JR-35-2511</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Metagenomics</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Trip 5</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="L36" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="M36" t="n">
+        <v>423</v>
+      </c>
+      <c r="N36" t="n">
+        <v>235</v>
+      </c>
+      <c r="O36" t="n">
+        <v>9.800000000000001</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>A10</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Pretoria (Upstream)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Apies River</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>-25.6780</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>28.1940</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>SAMP-036</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>AR-36-2511</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>WGS</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Trip 5</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="L37" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="M37" t="n">
+        <v>566</v>
+      </c>
+      <c r="N37" t="n">
+        <v>765</v>
+      </c>
+      <c r="O37" t="n">
+        <v>10.1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>E16</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Sandton</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Jukskei River</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>-26.0950</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>28.0550</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>SAMP-037</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>JR-37-2601</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Metagenomics</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Trip 6</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="L38" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="M38" t="n">
+        <v>189</v>
+      </c>
+      <c r="N38" t="n">
+        <v>937</v>
+      </c>
+      <c r="O38" t="n">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>F04</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Benoni</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Blesbokspruit</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>-26.1870</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>28.3200</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>SAMP-038</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>B-38-2601</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Metagenomics</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Trip 6</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="L39" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="M39" t="n">
+        <v>204</v>
+      </c>
+      <c r="N39" t="n">
+        <v>607</v>
+      </c>
+      <c r="O39" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>C02</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Midrand</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Hennops River</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>-25.9940</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>28.1320</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>SAMP-039</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>HR-39-2601</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>WGS</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Trip 6</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>25</v>
+      </c>
+      <c r="L40" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="M40" t="n">
+        <v>516</v>
+      </c>
+      <c r="N40" t="n">
+        <v>701</v>
+      </c>
+      <c r="O40" t="n">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>C03</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Kyalami</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Hennops River</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>-26.0220</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>28.0680</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>SAMP-040</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>HR-40-2601</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>16S rRNA</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Trip 6</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
         <v>24</v>
       </c>
-      <c r="K2" t="s" s="3">
-        <v>25</v>
-      </c>
-      <c r="L2" t="s" s="3">
-        <v>26</v>
-      </c>
-      <c r="M2" s="4">
-        <v>250</v>
-      </c>
-      <c r="N2" s="4">
-        <v>400</v>
-      </c>
-      <c r="O2" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" ht="46.35" customHeight="1">
-      <c r="A3" t="s" s="3">
-        <v>28</v>
-      </c>
-      <c r="B3" t="s" s="3">
-        <v>29</v>
-      </c>
-      <c r="C3" t="s" s="3">
-        <v>17</v>
-      </c>
-      <c r="D3" t="s" s="3">
-        <v>30</v>
-      </c>
-      <c r="E3" t="s" s="3">
-        <v>31</v>
-      </c>
-      <c r="F3" t="s" s="3">
-        <v>32</v>
-      </c>
-      <c r="G3" t="s" s="3">
-        <v>33</v>
-      </c>
-      <c r="H3" t="s" s="3">
-        <v>34</v>
-      </c>
-      <c r="I3" t="s" s="3">
-        <v>23</v>
-      </c>
-      <c r="J3" t="s" s="3">
-        <v>24</v>
-      </c>
-      <c r="K3" t="s" s="3">
-        <v>35</v>
-      </c>
-      <c r="L3" t="s" s="3">
-        <v>36</v>
-      </c>
-      <c r="M3" s="4">
-        <v>260</v>
-      </c>
-      <c r="N3" s="4">
-        <v>410</v>
-      </c>
-      <c r="O3" t="s" s="3">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" ht="60.35" customHeight="1">
-      <c r="A4" t="s" s="3">
-        <v>38</v>
-      </c>
-      <c r="B4" t="s" s="3">
-        <v>39</v>
-      </c>
-      <c r="C4" t="s" s="3">
-        <v>17</v>
-      </c>
-      <c r="D4" t="s" s="3">
-        <v>40</v>
-      </c>
-      <c r="E4" t="s" s="3">
-        <v>41</v>
-      </c>
-      <c r="F4" t="s" s="3">
-        <v>42</v>
-      </c>
-      <c r="G4" t="s" s="3">
-        <v>43</v>
-      </c>
-      <c r="H4" t="s" s="3">
-        <v>34</v>
-      </c>
-      <c r="I4" t="s" s="3">
-        <v>44</v>
-      </c>
-      <c r="J4" t="s" s="3">
-        <v>45</v>
-      </c>
-      <c r="K4" t="s" s="3">
-        <v>46</v>
-      </c>
-      <c r="L4" t="s" s="3">
-        <v>47</v>
-      </c>
-      <c r="M4" s="4">
-        <v>280</v>
-      </c>
-      <c r="N4" s="4">
-        <v>450</v>
-      </c>
-      <c r="O4" t="s" s="3">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" ht="46.35" customHeight="1">
-      <c r="A5" s="5"/>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
-      <c r="N5" s="5"/>
-      <c r="O5" s="5"/>
-    </row>
-    <row r="6" ht="20.05" customHeight="1">
-      <c r="A6" s="5"/>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="5"/>
-      <c r="O6" s="5"/>
-    </row>
-    <row r="7" ht="20.05" customHeight="1">
-      <c r="A7" s="5"/>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5"/>
-      <c r="M7" s="5"/>
-      <c r="N7" s="5"/>
-      <c r="O7" s="5"/>
-    </row>
-    <row r="8" ht="20.05" customHeight="1">
-      <c r="A8" s="5"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5"/>
-      <c r="M8" s="5"/>
-      <c r="N8" s="5"/>
-      <c r="O8" s="5"/>
-    </row>
-    <row r="9" ht="20.05" customHeight="1">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
-      <c r="L9" s="5"/>
-      <c r="M9" s="5"/>
-      <c r="N9" s="5"/>
-      <c r="O9" s="5"/>
-    </row>
-    <row r="10" ht="20.05" customHeight="1">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5"/>
-      <c r="L10" s="5"/>
-      <c r="M10" s="5"/>
-      <c r="N10" s="5"/>
-      <c r="O10" s="5"/>
-    </row>
-    <row r="11" ht="20.05" customHeight="1">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="5"/>
-      <c r="L11" s="5"/>
-      <c r="M11" s="5"/>
-      <c r="N11" s="5"/>
-      <c r="O11" s="5"/>
-    </row>
-    <row r="12" ht="20.05" customHeight="1">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="5"/>
-      <c r="L12" s="5"/>
-      <c r="M12" s="5"/>
-      <c r="N12" s="5"/>
-      <c r="O12" s="5"/>
-    </row>
-    <row r="13" ht="20.05" customHeight="1">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="5"/>
-      <c r="L13" s="5"/>
-      <c r="M13" s="5"/>
-      <c r="N13" s="5"/>
-      <c r="O13" s="5"/>
-    </row>
-    <row r="14" ht="20.05" customHeight="1">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="5"/>
-      <c r="L14" s="5"/>
-      <c r="M14" s="5"/>
-      <c r="N14" s="5"/>
-      <c r="O14" s="5"/>
-    </row>
-    <row r="15" ht="20.05" customHeight="1">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
-      <c r="K15" s="5"/>
-      <c r="L15" s="5"/>
-      <c r="M15" s="5"/>
-      <c r="N15" s="5"/>
-      <c r="O15" s="5"/>
-    </row>
-    <row r="16" ht="20.05" customHeight="1">
-      <c r="A16" s="5"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
-      <c r="J16" s="5"/>
-      <c r="K16" s="5"/>
-      <c r="L16" s="5"/>
-      <c r="M16" s="5"/>
-      <c r="N16" s="5"/>
-      <c r="O16" s="5"/>
-    </row>
-    <row r="17" ht="20.05" customHeight="1">
-      <c r="A17" s="5"/>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-      <c r="I17" s="5"/>
-      <c r="J17" s="5"/>
-      <c r="K17" s="5"/>
-      <c r="L17" s="5"/>
-      <c r="M17" s="5"/>
-      <c r="N17" s="5"/>
-      <c r="O17" s="5"/>
-    </row>
-    <row r="18" ht="20.05" customHeight="1">
-      <c r="A18" s="5"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5"/>
-      <c r="I18" s="5"/>
-      <c r="J18" s="5"/>
-      <c r="K18" s="5"/>
-      <c r="L18" s="5"/>
-      <c r="M18" s="5"/>
-      <c r="N18" s="5"/>
-      <c r="O18" s="5"/>
-    </row>
-    <row r="19" ht="20.05" customHeight="1">
-      <c r="A19" s="5"/>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
-      <c r="I19" s="5"/>
-      <c r="J19" s="5"/>
-      <c r="K19" s="5"/>
-      <c r="L19" s="5"/>
-      <c r="M19" s="5"/>
-      <c r="N19" s="5"/>
-      <c r="O19" s="5"/>
-    </row>
-    <row r="20" ht="20.05" customHeight="1">
-      <c r="A20" s="5"/>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-      <c r="H20" s="5"/>
-      <c r="I20" s="5"/>
-      <c r="J20" s="5"/>
-      <c r="K20" s="5"/>
-      <c r="L20" s="5"/>
-      <c r="M20" s="5"/>
-      <c r="N20" s="5"/>
-      <c r="O20" s="5"/>
-    </row>
-    <row r="21" ht="20.05" customHeight="1">
-      <c r="A21" s="5"/>
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
-      <c r="I21" s="5"/>
-      <c r="J21" s="5"/>
-      <c r="K21" s="5"/>
-      <c r="L21" s="5"/>
-      <c r="M21" s="5"/>
-      <c r="N21" s="5"/>
-      <c r="O21" s="5"/>
-    </row>
-    <row r="22" ht="20.05" customHeight="1">
-      <c r="A22" s="5"/>
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-      <c r="H22" s="5"/>
-      <c r="I22" s="5"/>
-      <c r="J22" s="5"/>
-      <c r="K22" s="5"/>
-      <c r="L22" s="5"/>
-      <c r="M22" s="5"/>
-      <c r="N22" s="5"/>
-      <c r="O22" s="5"/>
+      <c r="L41" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="M41" t="n">
+        <v>363</v>
+      </c>
+      <c r="N41" t="n">
+        <v>924</v>
+      </c>
+      <c r="O41" t="n">
+        <v>9.4</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>E17</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Lanseria</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Jukskei River</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>-25.9380</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>27.9260</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>SAMP-041</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>JR-41-2601</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>WGS</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Trip 6</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="L42" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="M42" t="n">
+        <v>162</v>
+      </c>
+      <c r="N42" t="n">
+        <v>281</v>
+      </c>
+      <c r="O42" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>B26</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Hammanskraal</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Apies River</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>-25.4080</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>28.2710</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>SAMP-042</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>AR-42-2601</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>16S rRNA</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Trip 6</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="L43" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="M43" t="n">
+        <v>291</v>
+      </c>
+      <c r="N43" t="n">
+        <v>570</v>
+      </c>
+      <c r="O43" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>A12</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Pretoria (Downstream)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Apies River</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>-25.8100</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>28.2650</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>SAMP-043</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>AR-43-2601</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Shotgun</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Trip 6</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="L44" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="M44" t="n">
+        <v>305</v>
+      </c>
+      <c r="N44" t="n">
+        <v>639</v>
+      </c>
+      <c r="O44" t="n">
+        <v>4.2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.277778" footer="0.277778"/>
-  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="72" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
+  <pageSetup orientation="portrait" scale="72" fitToHeight="1" fitToWidth="1" firstPageNumber="1" useFirstPageNumber="0" pageOrder="downThenOver"/>
   <headerFooter>
-    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12 &amp;K000000&amp;P</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
   </headerFooter>
 </worksheet>
 </file>